--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/100.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/100.xlsx
@@ -426,13 +426,13 @@
         <v>12.83456853187131</v>
       </c>
       <c r="E2">
-        <v>-19.72375703169382</v>
+        <v>-18.4167488636</v>
       </c>
       <c r="F2">
-        <v>-5.078560818902536</v>
+        <v>-3.696635242447456</v>
       </c>
       <c r="G2">
-        <v>-11.30859118673763</v>
+        <v>-11.12186343023275</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>12.29397857023153</v>
       </c>
       <c r="E3">
-        <v>-19.67181543482584</v>
+        <v>-18.1199572056113</v>
       </c>
       <c r="F3">
-        <v>-5.078636200336192</v>
+        <v>-3.880162525639895</v>
       </c>
       <c r="G3">
-        <v>-12.01432288218612</v>
+        <v>-11.53643921182547</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>11.71694422148042</v>
       </c>
       <c r="E4">
-        <v>-19.94650361118311</v>
+        <v>-17.4208242174631</v>
       </c>
       <c r="F4">
-        <v>-5.319521299233274</v>
+        <v>-4.012824736830832</v>
       </c>
       <c r="G4">
-        <v>-12.14411160096996</v>
+        <v>-10.98279869810037</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>11.18951597226434</v>
       </c>
       <c r="E5">
-        <v>-19.8876334490834</v>
+        <v>-16.48354330972553</v>
       </c>
       <c r="F5">
-        <v>-4.721202292967427</v>
+        <v>-4.305992244355606</v>
       </c>
       <c r="G5">
-        <v>-12.05838968772946</v>
+        <v>-12.04963538860886</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>10.72238588288725</v>
       </c>
       <c r="E6">
-        <v>-20.09968377296657</v>
+        <v>-19.15943218627996</v>
       </c>
       <c r="F6">
-        <v>-5.058830764102658</v>
+        <v>-3.329899597512656</v>
       </c>
       <c r="G6">
-        <v>-12.75195789485709</v>
+        <v>-12.94792885249493</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>10.36585296339575</v>
       </c>
       <c r="E7">
-        <v>-20.3840357128562</v>
+        <v>-18.43484917420866</v>
       </c>
       <c r="F7">
-        <v>-4.93540070761592</v>
+        <v>-2.156098845908742</v>
       </c>
       <c r="G7">
-        <v>-12.80660663992964</v>
+        <v>-10.98888208287158</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>10.14652935179497</v>
       </c>
       <c r="E8">
-        <v>-21.97556790285195</v>
+        <v>-17.52228467760495</v>
       </c>
       <c r="F8">
-        <v>-4.348361580273995</v>
+        <v>-3.335694027495238</v>
       </c>
       <c r="G8">
-        <v>-12.31799665629117</v>
+        <v>-13.53570063288138</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>10.07016748387966</v>
       </c>
       <c r="E9">
-        <v>-21.95961861739694</v>
+        <v>-18.77917169538188</v>
       </c>
       <c r="F9">
-        <v>-4.42212769749329</v>
+        <v>-2.849444847154137</v>
       </c>
       <c r="G9">
-        <v>-12.12408630579266</v>
+        <v>-11.24469267808901</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>10.13713206440312</v>
       </c>
       <c r="E10">
-        <v>-20.43445574245761</v>
+        <v>-20.01346162786053</v>
       </c>
       <c r="F10">
-        <v>-4.226475600626076</v>
+        <v>-2.706016344829014</v>
       </c>
       <c r="G10">
-        <v>-12.72397563739815</v>
+        <v>-13.12226015394822</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>10.35204522720773</v>
       </c>
       <c r="E11">
-        <v>-21.73465308564389</v>
+        <v>-20.28072310684521</v>
       </c>
       <c r="F11">
-        <v>-3.773236861286534</v>
+        <v>-2.397649123830272</v>
       </c>
       <c r="G11">
-        <v>-11.82869105368209</v>
+        <v>-12.12751518232228</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>10.68890089269997</v>
       </c>
       <c r="E12">
-        <v>-22.47289397532233</v>
+        <v>-21.7944063001751</v>
       </c>
       <c r="F12">
-        <v>-4.012024533919728</v>
+        <v>-2.623273210065579</v>
       </c>
       <c r="G12">
-        <v>-10.78759554630744</v>
+        <v>-12.14795719263762</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>11.10699062946372</v>
       </c>
       <c r="E13">
-        <v>-24.6368796215757</v>
+        <v>-23.66693030234679</v>
       </c>
       <c r="F13">
-        <v>-3.868597688329411</v>
+        <v>-2.785305187522774</v>
       </c>
       <c r="G13">
-        <v>-11.57335295436923</v>
+        <v>-11.5601755685865</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>11.5847672828093</v>
       </c>
       <c r="E14">
-        <v>-25.3725030532777</v>
+        <v>-23.3732768768454</v>
       </c>
       <c r="F14">
-        <v>-3.54116890502485</v>
+        <v>-2.66400072179162</v>
       </c>
       <c r="G14">
-        <v>-10.18590482406583</v>
+        <v>-10.39911203855542</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>12.0768904183532</v>
       </c>
       <c r="E15">
-        <v>-24.41227636774326</v>
+        <v>-25.09475362849125</v>
       </c>
       <c r="F15">
-        <v>-3.283050450679927</v>
+        <v>-1.865773466942974</v>
       </c>
       <c r="G15">
-        <v>-11.73512045847141</v>
+        <v>-12.24413964020963</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>12.52620380975321</v>
       </c>
       <c r="E16">
-        <v>-26.82210381092505</v>
+        <v>-22.02356519885925</v>
       </c>
       <c r="F16">
-        <v>-2.910244529417412</v>
+        <v>-1.354628532678136</v>
       </c>
       <c r="G16">
-        <v>-10.29359779686836</v>
+        <v>-10.68111006303878</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>12.90556409945787</v>
       </c>
       <c r="E17">
-        <v>-26.21102247138199</v>
+        <v>-24.08824593859842</v>
       </c>
       <c r="F17">
-        <v>-3.030131658522376</v>
+        <v>-2.0205356920732</v>
       </c>
       <c r="G17">
-        <v>-10.08107635768468</v>
+        <v>-8.702326745735373</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>13.18476196184148</v>
       </c>
       <c r="E18">
-        <v>-27.97730847333374</v>
+        <v>-26.22368861318144</v>
       </c>
       <c r="F18">
-        <v>-2.76338989951431</v>
+        <v>-1.025133801070994</v>
       </c>
       <c r="G18">
-        <v>-9.552412502470071</v>
+        <v>-9.173040946988634</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>13.32977528317616</v>
       </c>
       <c r="E19">
-        <v>-28.50062798660814</v>
+        <v>-25.98619279384917</v>
       </c>
       <c r="F19">
-        <v>-2.996929864650769</v>
+        <v>-1.276020607989477</v>
       </c>
       <c r="G19">
-        <v>-9.727180206390775</v>
+        <v>-9.199438374434367</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>13.3377312044557</v>
       </c>
       <c r="E20">
-        <v>-28.71843400095506</v>
+        <v>-27.90459023771857</v>
       </c>
       <c r="F20">
-        <v>-2.034385166680605</v>
+        <v>-0.4659510127504101</v>
       </c>
       <c r="G20">
-        <v>-9.785382514412206</v>
+        <v>-7.939052267798902</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>13.21491337308315</v>
       </c>
       <c r="E21">
-        <v>-29.01697817838474</v>
+        <v>-27.77793334819803</v>
       </c>
       <c r="F21">
-        <v>-1.988014816206694</v>
+        <v>0.0001166525562869781</v>
       </c>
       <c r="G21">
-        <v>-10.23609767026065</v>
+        <v>-8.762120446213133</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>12.9642432022401</v>
       </c>
       <c r="E22">
-        <v>-29.4694882078382</v>
+        <v>-26.97370353527982</v>
       </c>
       <c r="F22">
-        <v>-2.14264367418507</v>
+        <v>-1.335471708120995</v>
       </c>
       <c r="G22">
-        <v>-9.699539195974014</v>
+        <v>-6.678918815223516</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>12.6027528891134</v>
       </c>
       <c r="E23">
-        <v>-29.77809691874992</v>
+        <v>-29.4887364866078</v>
       </c>
       <c r="F23">
-        <v>-1.914135212653215</v>
+        <v>0.2636103829779761</v>
       </c>
       <c r="G23">
-        <v>-9.96020928032098</v>
+        <v>-8.616375146985719</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>12.16512431831538</v>
       </c>
       <c r="E24">
-        <v>-31.18222953312325</v>
+        <v>-28.19300874726709</v>
       </c>
       <c r="F24">
-        <v>-1.771083617496366</v>
+        <v>0.2575450768546781</v>
       </c>
       <c r="G24">
-        <v>-10.17789864346078</v>
+        <v>-9.712775643744813</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>11.67617060976313</v>
       </c>
       <c r="E25">
-        <v>-30.42012358542439</v>
+        <v>-29.7379361470129</v>
       </c>
       <c r="F25">
-        <v>-1.638495959371679</v>
+        <v>0.007231500178931932</v>
       </c>
       <c r="G25">
-        <v>-10.2489174028934</v>
+        <v>-8.625136008549436</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>11.15475127616615</v>
       </c>
       <c r="E26">
-        <v>-30.52477888397866</v>
+        <v>-28.46856639063383</v>
       </c>
       <c r="F26">
-        <v>-2.544803622733188</v>
+        <v>0.4078308045401757</v>
       </c>
       <c r="G26">
-        <v>-10.18819511671432</v>
+        <v>-8.177026142619189</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>10.64319164870356</v>
       </c>
       <c r="E27">
-        <v>-30.09132240891247</v>
+        <v>-30.30968089708832</v>
       </c>
       <c r="F27">
-        <v>-1.703635458458221</v>
+        <v>0.06010784823442997</v>
       </c>
       <c r="G27">
-        <v>-10.32257754568138</v>
+        <v>-8.243923687773149</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>10.16669757170262</v>
       </c>
       <c r="E28">
-        <v>-30.36451845308421</v>
+        <v>-31.48031180620415</v>
       </c>
       <c r="F28">
-        <v>-1.632967435325396</v>
+        <v>0.283979937412816</v>
       </c>
       <c r="G28">
-        <v>-9.783289095057281</v>
+        <v>-8.403748708712142</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>9.735632735076258</v>
       </c>
       <c r="E29">
-        <v>-30.46167459868177</v>
+        <v>-30.52538343525868</v>
       </c>
       <c r="F29">
-        <v>-1.972489554343426</v>
+        <v>0.3766436001921771</v>
       </c>
       <c r="G29">
-        <v>-9.942113343420642</v>
+        <v>-8.984679142147151</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>9.383309434348874</v>
       </c>
       <c r="E30">
-        <v>-30.58574799378093</v>
+        <v>-29.29415248697222</v>
       </c>
       <c r="F30">
-        <v>-1.985480011954128</v>
+        <v>0.8126688649015444</v>
       </c>
       <c r="G30">
-        <v>-9.387583618652926</v>
+        <v>-7.135238297495492</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>9.128752387813005</v>
       </c>
       <c r="E31">
-        <v>-29.81953924863112</v>
+        <v>-27.58758347175962</v>
       </c>
       <c r="F31">
-        <v>-1.763936463545011</v>
+        <v>0.078823981333282</v>
       </c>
       <c r="G31">
-        <v>-9.375912313565982</v>
+        <v>-8.579422029783252</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>8.96838260741227</v>
       </c>
       <c r="E32">
-        <v>-29.84356280324181</v>
+        <v>-27.95746470023213</v>
       </c>
       <c r="F32">
-        <v>-2.077136379971685</v>
+        <v>0.1703370417901546</v>
       </c>
       <c r="G32">
-        <v>-8.341484248400118</v>
+        <v>-8.215603464493581</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>8.912170942641422</v>
       </c>
       <c r="E33">
-        <v>-28.7870630245413</v>
+        <v>-26.62754245365949</v>
       </c>
       <c r="F33">
-        <v>-2.067765887911217</v>
+        <v>-0.4033546015904626</v>
       </c>
       <c r="G33">
-        <v>-9.04057475141229</v>
+        <v>-7.089977127304512</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>8.963168384292606</v>
       </c>
       <c r="E34">
-        <v>-29.64995468975487</v>
+        <v>-28.42014341806981</v>
       </c>
       <c r="F34">
-        <v>-2.563576913182833</v>
+        <v>-0.5140808155878669</v>
       </c>
       <c r="G34">
-        <v>-9.073938212228725</v>
+        <v>-7.642613587232429</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>9.101528517026237</v>
       </c>
       <c r="E35">
-        <v>-27.63740574279201</v>
+        <v>-27.49160246516704</v>
       </c>
       <c r="F35">
-        <v>-2.023995782714694</v>
+        <v>-0.2071557822373997</v>
       </c>
       <c r="G35">
-        <v>-9.176906225985659</v>
+        <v>-8.663171928866518</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>9.307610813966896</v>
       </c>
       <c r="E36">
-        <v>-27.56252289660117</v>
+        <v>-27.30248886213272</v>
       </c>
       <c r="F36">
-        <v>-2.060578143957125</v>
+        <v>-0.6605800758751679</v>
       </c>
       <c r="G36">
-        <v>-9.002013835645696</v>
+        <v>-8.186252937644348</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>9.573106691482131</v>
       </c>
       <c r="E37">
-        <v>-27.01817767850915</v>
+        <v>-28.85339611180566</v>
       </c>
       <c r="F37">
-        <v>-2.097009742332248</v>
+        <v>-0.2178831401036533</v>
       </c>
       <c r="G37">
-        <v>-9.269577766489057</v>
+        <v>-6.612162362596613</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>9.873190352569573</v>
       </c>
       <c r="E38">
-        <v>-26.16788422798492</v>
+        <v>-24.70098469962828</v>
       </c>
       <c r="F38">
-        <v>-2.214903819466076</v>
+        <v>-0.4404215577635321</v>
       </c>
       <c r="G38">
-        <v>-9.078646765166528</v>
+        <v>-7.993218673302215</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>10.17798300653222</v>
       </c>
       <c r="E39">
-        <v>-26.07443916683664</v>
+        <v>-25.64401676935559</v>
       </c>
       <c r="F39">
-        <v>-2.008994049049995</v>
+        <v>0.1128176944419653</v>
       </c>
       <c r="G39">
-        <v>-9.193371395770953</v>
+        <v>-7.965177353855201</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>10.48511161392797</v>
       </c>
       <c r="E40">
-        <v>-24.47295791944605</v>
+        <v>-24.40884378444545</v>
       </c>
       <c r="F40">
-        <v>-1.936593909677915</v>
+        <v>0.2329442217263384</v>
       </c>
       <c r="G40">
-        <v>-8.919792985809131</v>
+        <v>-7.227027189399399</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>10.78156412932742</v>
       </c>
       <c r="E41">
-        <v>-24.20352730141168</v>
+        <v>-26.53719486873246</v>
       </c>
       <c r="F41">
-        <v>-2.283587902669197</v>
+        <v>-0.5707659969614371</v>
       </c>
       <c r="G41">
-        <v>-9.52938488956589</v>
+        <v>-8.226798992454407</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>11.04545716485352</v>
       </c>
       <c r="E42">
-        <v>-24.62602034090531</v>
+        <v>-24.34728370878518</v>
       </c>
       <c r="F42">
-        <v>-2.427785129944118</v>
+        <v>-0.05290631652950658</v>
       </c>
       <c r="G42">
-        <v>-10.028655562051</v>
+        <v>-7.457641284261852</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>11.28400493074037</v>
       </c>
       <c r="E43">
-        <v>-22.49231207186722</v>
+        <v>-23.70114745194875</v>
       </c>
       <c r="F43">
-        <v>-1.871150399754546</v>
+        <v>-0.07306132380702135</v>
       </c>
       <c r="G43">
-        <v>-9.540304794915722</v>
+        <v>-8.698769901564935</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>11.49935233469731</v>
       </c>
       <c r="E44">
-        <v>-21.86795777500768</v>
+        <v>-22.89461264576063</v>
       </c>
       <c r="F44">
-        <v>-2.005977134968999</v>
+        <v>-0.1372987307919146</v>
       </c>
       <c r="G44">
-        <v>-9.542414620378445</v>
+        <v>-8.799854494146748</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>11.68046827035317</v>
       </c>
       <c r="E45">
-        <v>-22.19649403579016</v>
+        <v>-23.56432866675501</v>
       </c>
       <c r="F45">
-        <v>-1.797182160888967</v>
+        <v>-0.7566930605197861</v>
       </c>
       <c r="G45">
-        <v>-9.765695185055538</v>
+        <v>-7.909737834386823</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>11.83551475789583</v>
       </c>
       <c r="E46">
-        <v>-21.82381873885492</v>
+        <v>-21.49950301584759</v>
       </c>
       <c r="F46">
-        <v>-1.662104430351465</v>
+        <v>0.1519853903485343</v>
       </c>
       <c r="G46">
-        <v>-8.931401947686446</v>
+        <v>-7.732735618584138</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>11.97458102837684</v>
       </c>
       <c r="E47">
-        <v>-21.40394768581174</v>
+        <v>-21.01248375021867</v>
       </c>
       <c r="F47">
-        <v>-2.277307221021172</v>
+        <v>-0.8014497512930434</v>
       </c>
       <c r="G47">
-        <v>-8.727533089755028</v>
+        <v>-6.968037090490868</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>12.09321123821673</v>
       </c>
       <c r="E48">
-        <v>-18.99478592830908</v>
+        <v>-17.14654360376652</v>
       </c>
       <c r="F48">
-        <v>-1.733552775577728</v>
+        <v>0.1049879657507044</v>
       </c>
       <c r="G48">
-        <v>-8.626264748765884</v>
+        <v>-7.853031763396499</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>12.18988451281574</v>
       </c>
       <c r="E49">
-        <v>-20.23276656710398</v>
+        <v>-18.97694374071886</v>
       </c>
       <c r="F49">
-        <v>-1.742173595138663</v>
+        <v>-0.5570681135887445</v>
       </c>
       <c r="G49">
-        <v>-9.052790739278104</v>
+        <v>-8.061897921762952</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>12.27763543273413</v>
       </c>
       <c r="E50">
-        <v>-18.94115068216224</v>
+        <v>-19.33504187982341</v>
       </c>
       <c r="F50">
-        <v>-2.063609968651372</v>
+        <v>0.01587717076195037</v>
       </c>
       <c r="G50">
-        <v>-9.328902252283816</v>
+        <v>-8.157752247179012</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>12.35381375701078</v>
       </c>
       <c r="E51">
-        <v>-18.55546960787697</v>
+        <v>-18.79260767776264</v>
       </c>
       <c r="F51">
-        <v>-1.738581794080124</v>
+        <v>-0.1381378669709505</v>
       </c>
       <c r="G51">
-        <v>-9.433366503071857</v>
+        <v>-8.332060580081393</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>12.40657162105257</v>
       </c>
       <c r="E52">
-        <v>-18.23067386662483</v>
+        <v>-17.8122473967901</v>
       </c>
       <c r="F52">
-        <v>-1.309704511689514</v>
+        <v>-0.1831712324567428</v>
       </c>
       <c r="G52">
-        <v>-9.164348991077665</v>
+        <v>-7.178025426630652</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>12.44845372056225</v>
       </c>
       <c r="E53">
-        <v>-17.01706547493921</v>
+        <v>-15.52141466510787</v>
       </c>
       <c r="F53">
-        <v>-1.655103069063004</v>
+        <v>0.1703743183232806</v>
       </c>
       <c r="G53">
-        <v>-9.286374339651854</v>
+        <v>-7.679366549919769</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>12.47711889656855</v>
       </c>
       <c r="E54">
-        <v>-17.47831319499047</v>
+        <v>-17.53419456424513</v>
       </c>
       <c r="F54">
-        <v>-1.517480593864103</v>
+        <v>-0.9420518640398147</v>
       </c>
       <c r="G54">
-        <v>-8.982956500828442</v>
+        <v>-7.911299695849119</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>12.47536501303814</v>
       </c>
       <c r="E55">
-        <v>-16.71584044089699</v>
+        <v>-16.29611429902206</v>
       </c>
       <c r="F55">
-        <v>-1.274905625465309</v>
+        <v>-0.344361588632693</v>
       </c>
       <c r="G55">
-        <v>-9.478407831418355</v>
+        <v>-7.836589562162122</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>12.45266912144928</v>
       </c>
       <c r="E56">
-        <v>-14.95957142345021</v>
+        <v>-16.17583802937833</v>
       </c>
       <c r="F56">
-        <v>-1.241736966289814</v>
+        <v>-0.333045261543049</v>
       </c>
       <c r="G56">
-        <v>-9.626925762863502</v>
+        <v>-8.412489882946502</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>12.41135751676806</v>
       </c>
       <c r="E57">
-        <v>-14.56216160148508</v>
+        <v>-16.03296920291034</v>
       </c>
       <c r="F57">
-        <v>-1.722275381756016</v>
+        <v>0.2221124895673321</v>
       </c>
       <c r="G57">
-        <v>-9.240132084214599</v>
+        <v>-8.834504193814483</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>12.33906112855838</v>
       </c>
       <c r="E58">
-        <v>-14.53274010585724</v>
+        <v>-14.19151053243127</v>
       </c>
       <c r="F58">
-        <v>-1.743834471781276</v>
+        <v>-0.01614834139768132</v>
       </c>
       <c r="G58">
-        <v>-9.612061829199217</v>
+        <v>-9.030114217080781</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>12.24213097600998</v>
       </c>
       <c r="E59">
-        <v>-14.97871781155464</v>
+        <v>-15.46309697683709</v>
       </c>
       <c r="F59">
-        <v>-1.399154108946013</v>
+        <v>0.364749072655379</v>
       </c>
       <c r="G59">
-        <v>-9.335694380911868</v>
+        <v>-8.772738479179496</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>12.1331270196342</v>
       </c>
       <c r="E60">
-        <v>-13.87073607609794</v>
+        <v>-12.59367923509085</v>
       </c>
       <c r="F60">
-        <v>-1.483891952415388</v>
+        <v>-0.346531082860625</v>
       </c>
       <c r="G60">
-        <v>-9.998107389332567</v>
+        <v>-9.720158392253564</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>12.01105734995765</v>
       </c>
       <c r="E61">
-        <v>-12.93244531865665</v>
+        <v>-14.60769993610621</v>
       </c>
       <c r="F61">
-        <v>-1.752490082773128</v>
+        <v>-0.832930197701633</v>
       </c>
       <c r="G61">
-        <v>-9.916132631112959</v>
+        <v>-9.399028519452269</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>11.87875500980436</v>
       </c>
       <c r="E62">
-        <v>-12.80644505786723</v>
+        <v>-13.21139931752915</v>
       </c>
       <c r="F62">
-        <v>-1.588413694565824</v>
+        <v>-0.6584669106306263</v>
       </c>
       <c r="G62">
-        <v>-9.95353527566907</v>
+        <v>-9.246356561512867</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>11.76045381652927</v>
       </c>
       <c r="E63">
-        <v>-13.29628556280293</v>
+        <v>-13.7023357131747</v>
       </c>
       <c r="F63">
-        <v>-1.330011110201741</v>
+        <v>-0.4111835019143207</v>
       </c>
       <c r="G63">
-        <v>-9.831710081610007</v>
+        <v>-10.28430865863357</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>11.66440719148936</v>
       </c>
       <c r="E64">
-        <v>-12.42428260788593</v>
+        <v>-14.22988482117227</v>
       </c>
       <c r="F64">
-        <v>-1.727894197849205</v>
+        <v>0.1750057204723326</v>
       </c>
       <c r="G64">
-        <v>-10.32925811277641</v>
+        <v>-9.704329779450802</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>11.58896444919403</v>
       </c>
       <c r="E65">
-        <v>-13.29965474746464</v>
+        <v>-14.28571184873883</v>
       </c>
       <c r="F65">
-        <v>-1.794900837061657</v>
+        <v>-0.02464324911339024</v>
       </c>
       <c r="G65">
-        <v>-9.648145422688431</v>
+        <v>-9.867787112656101</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>11.56067579179021</v>
       </c>
       <c r="E66">
-        <v>-12.12011406573872</v>
+        <v>-11.19302675299242</v>
       </c>
       <c r="F66">
-        <v>-1.594522904161471</v>
+        <v>-0.3613058438569569</v>
       </c>
       <c r="G66">
-        <v>-10.25605077856364</v>
+        <v>-8.931037732093348</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>11.58913880462437</v>
       </c>
       <c r="E67">
-        <v>-12.15360213102545</v>
+        <v>-12.08427119396801</v>
       </c>
       <c r="F67">
-        <v>-1.6765544713259</v>
+        <v>-0.5453086099386028</v>
       </c>
       <c r="G67">
-        <v>-10.22875101518905</v>
+        <v>-9.864085894737046</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>11.66277260947679</v>
       </c>
       <c r="E68">
-        <v>-11.76760859203365</v>
+        <v>-14.15357550566901</v>
       </c>
       <c r="F68">
-        <v>-1.843249328893453</v>
+        <v>-0.2898599837329023</v>
       </c>
       <c r="G68">
-        <v>-10.91538600116157</v>
+        <v>-10.34817107384504</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>11.79551165258967</v>
       </c>
       <c r="E69">
-        <v>-11.98621161780592</v>
+        <v>-12.11041407441429</v>
       </c>
       <c r="F69">
-        <v>-1.916360207497134</v>
+        <v>-0.457692189744499</v>
       </c>
       <c r="G69">
-        <v>-9.821354546368399</v>
+        <v>-9.436345852247834</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>11.98803255172283</v>
       </c>
       <c r="E70">
-        <v>-12.21434255289033</v>
+        <v>-13.71753327194444</v>
       </c>
       <c r="F70">
-        <v>-1.797318013143026</v>
+        <v>-1.24935214782375</v>
       </c>
       <c r="G70">
-        <v>-9.772342939934973</v>
+        <v>-7.858009376502177</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>12.21855713076834</v>
       </c>
       <c r="E71">
-        <v>-11.56446577652356</v>
+        <v>-11.89347752707685</v>
       </c>
       <c r="F71">
-        <v>-2.494553199344564</v>
+        <v>-0.9216690557265301</v>
       </c>
       <c r="G71">
-        <v>-9.467530581948797</v>
+        <v>-11.09395007842656</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>12.47920707623398</v>
       </c>
       <c r="E72">
-        <v>-11.51579826636313</v>
+        <v>-11.09987604265464</v>
       </c>
       <c r="F72">
-        <v>-2.150929004947871</v>
+        <v>-1.495663053209169</v>
       </c>
       <c r="G72">
-        <v>-9.346784909782791</v>
+        <v>-9.684399639698736</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>12.76621424879156</v>
       </c>
       <c r="E73">
-        <v>-11.86820411364004</v>
+        <v>-11.45698244595151</v>
       </c>
       <c r="F73">
-        <v>-2.598520763702527</v>
+        <v>-1.456068748090158</v>
       </c>
       <c r="G73">
-        <v>-9.689675843966322</v>
+        <v>-9.815126787848573</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>13.05759671935539</v>
       </c>
       <c r="E74">
-        <v>-11.91635084928959</v>
+        <v>-14.31560883413747</v>
       </c>
       <c r="F74">
-        <v>-2.278500898448605</v>
+        <v>-2.05207246746518</v>
       </c>
       <c r="G74">
-        <v>-8.81172267252726</v>
+        <v>-9.088372305868722</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>13.33233655882316</v>
       </c>
       <c r="E75">
-        <v>-11.66977543957194</v>
+        <v>-14.57383600747685</v>
       </c>
       <c r="F75">
-        <v>-2.517177569849824</v>
+        <v>-1.27337894434195</v>
       </c>
       <c r="G75">
-        <v>-8.780114665245129</v>
+        <v>-9.492871456052388</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>13.59275986248069</v>
       </c>
       <c r="E76">
-        <v>-13.42016649775676</v>
+        <v>-11.55814402680885</v>
       </c>
       <c r="F76">
-        <v>-2.689830874145714</v>
+        <v>-2.03034770395936</v>
       </c>
       <c r="G76">
-        <v>-8.589882564114761</v>
+        <v>-7.755586045524111</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>13.82544950989227</v>
       </c>
       <c r="E77">
-        <v>-13.35413228977691</v>
+        <v>-13.55561315532618</v>
       </c>
       <c r="F77">
-        <v>-2.680328671668201</v>
+        <v>-1.686480797913646</v>
       </c>
       <c r="G77">
-        <v>-8.027120254454399</v>
+        <v>-6.664678313655526</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>14.00848532491</v>
       </c>
       <c r="E78">
-        <v>-13.20398167710458</v>
+        <v>-11.60582432963562</v>
       </c>
       <c r="F78">
-        <v>-3.0944668128608</v>
+        <v>-2.456165825531432</v>
       </c>
       <c r="G78">
-        <v>-7.749909532226271</v>
+        <v>-7.504300254837156</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>14.15072880889948</v>
       </c>
       <c r="E79">
-        <v>-14.1714584495253</v>
+        <v>-15.75963956875537</v>
       </c>
       <c r="F79">
-        <v>-2.967753936356768</v>
+        <v>-1.677743178548917</v>
       </c>
       <c r="G79">
-        <v>-7.234377125692555</v>
+        <v>-7.251098230759485</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>14.24901557720779</v>
       </c>
       <c r="E80">
-        <v>-14.54756180128435</v>
+        <v>-16.35324099862882</v>
       </c>
       <c r="F80">
-        <v>-2.889040809007953</v>
+        <v>-2.275200682715852</v>
       </c>
       <c r="G80">
-        <v>-6.706648418622383</v>
+        <v>-7.120948577604111</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>14.28477442364463</v>
       </c>
       <c r="E81">
-        <v>-14.03535063475076</v>
+        <v>-13.3012895265814</v>
       </c>
       <c r="F81">
-        <v>-3.397616147589307</v>
+        <v>-1.69489121215427</v>
       </c>
       <c r="G81">
-        <v>-6.134324629337798</v>
+        <v>-4.963410872185273</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>14.26863181896188</v>
       </c>
       <c r="E82">
-        <v>-14.88834305578357</v>
+        <v>-15.35483927720972</v>
       </c>
       <c r="F82">
-        <v>-3.78821705739876</v>
+        <v>-2.702096510278966</v>
       </c>
       <c r="G82">
-        <v>-7.184837242588059</v>
+        <v>-4.785716318633544</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>14.20513341613247</v>
       </c>
       <c r="E83">
-        <v>-16.18163900458216</v>
+        <v>-15.17088813454414</v>
       </c>
       <c r="F83">
-        <v>-3.727563167798378</v>
+        <v>-2.086462968559804</v>
       </c>
       <c r="G83">
-        <v>-6.671650909469346</v>
+        <v>-5.921035384309214</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>14.08456120469566</v>
       </c>
       <c r="E84">
-        <v>-17.4745500330901</v>
+        <v>-16.58813294540668</v>
       </c>
       <c r="F84">
-        <v>-3.877778484254637</v>
+        <v>-2.538783876817044</v>
       </c>
       <c r="G84">
-        <v>-6.145070629944979</v>
+        <v>-4.060927288367801</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>13.91095667164559</v>
       </c>
       <c r="E85">
-        <v>-17.9185759664902</v>
+        <v>-16.15946759584061</v>
       </c>
       <c r="F85">
-        <v>-3.759585366488398</v>
+        <v>-3.502369832612527</v>
       </c>
       <c r="G85">
-        <v>-5.507562093160466</v>
+        <v>-4.261708516811783</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>13.69611167704492</v>
       </c>
       <c r="E86">
-        <v>-18.07426037439989</v>
+        <v>-18.49908104953346</v>
       </c>
       <c r="F86">
-        <v>-4.331482766074552</v>
+        <v>-3.382777602302959</v>
       </c>
       <c r="G86">
-        <v>-6.157325992469506</v>
+        <v>-4.049328170155164</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>13.43658658214951</v>
       </c>
       <c r="E87">
-        <v>-19.04369344759192</v>
+        <v>-19.94332915090373</v>
       </c>
       <c r="F87">
-        <v>-4.360549349871384</v>
+        <v>-3.650661679959486</v>
       </c>
       <c r="G87">
-        <v>-4.765599149252589</v>
+        <v>-4.284795191704036</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>13.12663149740846</v>
       </c>
       <c r="E88">
-        <v>-20.94113311375382</v>
+        <v>-19.43677857687974</v>
       </c>
       <c r="F88">
-        <v>-4.485324675020268</v>
+        <v>-3.90843719019965</v>
       </c>
       <c r="G88">
-        <v>-5.06896120730949</v>
+        <v>-4.992590775513415</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>12.78302845583743</v>
       </c>
       <c r="E89">
-        <v>-20.95012666313305</v>
+        <v>-21.62119669785572</v>
       </c>
       <c r="F89">
-        <v>-4.904125696323224</v>
+        <v>-3.16714528368022</v>
       </c>
       <c r="G89">
-        <v>-4.90073625917832</v>
+        <v>-4.636174646061852</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>12.40527169361128</v>
       </c>
       <c r="E90">
-        <v>-22.46432610249981</v>
+        <v>-23.6348777633205</v>
       </c>
       <c r="F90">
-        <v>-5.314216434385745</v>
+        <v>-4.027760201103307</v>
       </c>
       <c r="G90">
-        <v>-4.936570479829015</v>
+        <v>-4.56132013862624</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>11.98383671195841</v>
       </c>
       <c r="E91">
-        <v>-24.8935806991745</v>
+        <v>-24.29773767466726</v>
       </c>
       <c r="F91">
-        <v>-5.612179360805325</v>
+        <v>-4.217232677145638</v>
       </c>
       <c r="G91">
-        <v>-4.68298127160733</v>
+        <v>-4.287951726844222</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>11.53331717514271</v>
       </c>
       <c r="E92">
-        <v>-25.59325257572961</v>
+        <v>-24.38392359198124</v>
       </c>
       <c r="F92">
-        <v>-6.12535048173741</v>
+        <v>-4.515425061335793</v>
       </c>
       <c r="G92">
-        <v>-4.452130928792598</v>
+        <v>-3.483360107031223</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>11.05633681650368</v>
       </c>
       <c r="E93">
-        <v>-27.25522970738868</v>
+        <v>-26.94539604425788</v>
       </c>
       <c r="F93">
-        <v>-6.39296326906952</v>
+        <v>-4.641123187771396</v>
       </c>
       <c r="G93">
-        <v>-4.864603447365714</v>
+        <v>-4.456918231047827</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>10.54243772203433</v>
       </c>
       <c r="E94">
-        <v>-28.99439920698249</v>
+        <v>-30.25907293581561</v>
       </c>
       <c r="F94">
-        <v>-6.568399059471413</v>
+        <v>-5.116079235310131</v>
       </c>
       <c r="G94">
-        <v>-5.67056989901212</v>
+        <v>-4.509660586394341</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>10.00277430202563</v>
       </c>
       <c r="E95">
-        <v>-30.5788239570232</v>
+        <v>-31.1485444792172</v>
       </c>
       <c r="F95">
-        <v>-6.951075392521985</v>
+        <v>-6.094433325162724</v>
       </c>
       <c r="G95">
-        <v>-5.602842204803621</v>
+        <v>-3.414109926019143</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>9.44036958563226</v>
       </c>
       <c r="E96">
-        <v>-33.15162665126703</v>
+        <v>-33.38374490771519</v>
       </c>
       <c r="F96">
-        <v>-7.490892607699922</v>
+        <v>-5.932255555042637</v>
       </c>
       <c r="G96">
-        <v>-5.292576456585648</v>
+        <v>-4.104971125360228</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>8.855690461536504</v>
       </c>
       <c r="E97">
-        <v>-34.26298436409645</v>
+        <v>-35.47777695173508</v>
       </c>
       <c r="F97">
-        <v>-7.633940061019758</v>
+        <v>-5.766807390416298</v>
       </c>
       <c r="G97">
-        <v>-6.157736145164436</v>
+        <v>-6.482944576364121</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>8.242325441446139</v>
       </c>
       <c r="E98">
-        <v>-36.14518345098553</v>
+        <v>-36.23634616123395</v>
       </c>
       <c r="F98">
-        <v>-8.067845947729063</v>
+        <v>-6.6097913360382</v>
       </c>
       <c r="G98">
-        <v>-6.957291089883687</v>
+        <v>-6.529724952137125</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>7.63030763192992</v>
       </c>
       <c r="E99">
-        <v>-39.12045653689807</v>
+        <v>-39.52608101071312</v>
       </c>
       <c r="F99">
-        <v>-8.038529611160287</v>
+        <v>-6.813065655562275</v>
       </c>
       <c r="G99">
-        <v>-7.38727876914112</v>
+        <v>-5.842023569157784</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>6.998155957329038</v>
       </c>
       <c r="E100">
-        <v>-40.02712043186978</v>
+        <v>-40.75020904751855</v>
       </c>
       <c r="F100">
-        <v>-8.600894572858724</v>
+        <v>-6.401852479668961</v>
       </c>
       <c r="G100">
-        <v>-7.23168980523537</v>
+        <v>-6.777640928282529</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>6.387353936532056</v>
       </c>
       <c r="E101">
-        <v>-42.14001583436862</v>
+        <v>-42.2167530906656</v>
       </c>
       <c r="F101">
-        <v>-8.633445684135433</v>
+        <v>-7.016159805176241</v>
       </c>
       <c r="G101">
-        <v>-7.843086380849823</v>
+        <v>-6.163688281073269</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>5.756097747646994</v>
       </c>
       <c r="E102">
-        <v>-43.36137018084435</v>
+        <v>-44.10972994569293</v>
       </c>
       <c r="F102">
-        <v>-8.524856658037251</v>
+        <v>-6.688076611623469</v>
       </c>
       <c r="G102">
-        <v>-8.203298883645664</v>
+        <v>-6.552116008058775</v>
       </c>
     </row>
   </sheetData>
